--- a/Output Files Qwen3.5 9B/LLM-Parameterized_Reference_Scoring_results_run_03.xlsx
+++ b/Output Files Qwen3.5 9B/LLM-Parameterized_Reference_Scoring_results_run_03.xlsx
@@ -39119,7 +39119,7 @@
         <v>1</v>
       </c>
       <c r="AD407" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="408">
@@ -39401,7 +39401,7 @@
         <v>2</v>
       </c>
       <c r="AD410" t="n">
-        <v>0.7959999999999999</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="411">
@@ -39589,7 +39589,7 @@
         <v>3</v>
       </c>
       <c r="AD412" t="n">
-        <v>0.7234999999999999</v>
+        <v>0.7235</v>
       </c>
     </row>
     <row r="413">
@@ -39871,7 +39871,7 @@
         <v>3</v>
       </c>
       <c r="AD415" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="416">
@@ -40153,7 +40153,7 @@
         <v>3</v>
       </c>
       <c r="AD418" t="n">
-        <v>0.7654999999999998</v>
+        <v>0.7655</v>
       </c>
     </row>
     <row r="419">
@@ -40529,7 +40529,7 @@
         <v>1</v>
       </c>
       <c r="AD422" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="423">
@@ -40614,7 +40614,7 @@
         <v>0.58</v>
       </c>
       <c r="AA423" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="AB423" t="n">
         <v>0.52</v>
@@ -40623,7 +40623,7 @@
         <v>2</v>
       </c>
       <c r="AD423" t="n">
-        <v>0.597</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="424">
@@ -40708,7 +40708,7 @@
         <v>0.38</v>
       </c>
       <c r="AA424" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB424" t="n">
         <v>0.67</v>
@@ -40717,7 +40717,7 @@
         <v>3</v>
       </c>
       <c r="AD424" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="425">
@@ -40999,7 +40999,7 @@
         <v>3</v>
       </c>
       <c r="AD427" t="n">
-        <v>0.7064999999999999</v>
+        <v>0.7065</v>
       </c>
     </row>
     <row r="428">
@@ -41093,7 +41093,7 @@
         <v>1</v>
       </c>
       <c r="AD428" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="429">
@@ -41272,7 +41272,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA430" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="AB430" t="n">
         <v>0.52</v>
@@ -41281,7 +41281,7 @@
         <v>3</v>
       </c>
       <c r="AD430" t="n">
-        <v>0.6775</v>
+        <v>0.6855</v>
       </c>
     </row>
     <row r="431">
@@ -41469,7 +41469,7 @@
         <v>2</v>
       </c>
       <c r="AD432" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="433">
@@ -41648,7 +41648,7 @@
         <v>0.64</v>
       </c>
       <c r="AA434" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AB434" t="n">
         <v>0.46</v>
@@ -41657,7 +41657,7 @@
         <v>1</v>
       </c>
       <c r="AD434" t="n">
-        <v>0.6240000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="435">
@@ -41742,7 +41742,7 @@
         <v>0.38</v>
       </c>
       <c r="AA435" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB435" t="n">
         <v>0.67</v>
@@ -41751,7 +41751,7 @@
         <v>2</v>
       </c>
       <c r="AD435" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="436">
@@ -41836,7 +41836,7 @@
         <v>0.13</v>
       </c>
       <c r="AA436" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="AB436" t="n">
         <v>0.48</v>
@@ -41845,7 +41845,7 @@
         <v>3</v>
       </c>
       <c r="AD436" t="n">
-        <v>0.2075</v>
+        <v>0.2335</v>
       </c>
     </row>
     <row r="437">
@@ -42221,7 +42221,7 @@
         <v>1</v>
       </c>
       <c r="AD440" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="441">
@@ -42306,7 +42306,7 @@
         <v>0.51</v>
       </c>
       <c r="AA441" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB441" t="n">
         <v>0.57</v>
@@ -42315,7 +42315,7 @@
         <v>2</v>
       </c>
       <c r="AD441" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="442">
@@ -42400,7 +42400,7 @@
         <v>0.19</v>
       </c>
       <c r="AA442" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB442" t="n">
         <v>0.52</v>
@@ -42409,7 +42409,7 @@
         <v>3</v>
       </c>
       <c r="AD442" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="443">
@@ -42597,7 +42597,7 @@
         <v>2</v>
       </c>
       <c r="AD444" t="n">
-        <v>0.6839999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="445">
@@ -42785,7 +42785,7 @@
         <v>1</v>
       </c>
       <c r="AD446" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="447">
@@ -42870,7 +42870,7 @@
         <v>0.51</v>
       </c>
       <c r="AA447" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB447" t="n">
         <v>0.57</v>
@@ -42879,7 +42879,7 @@
         <v>2</v>
       </c>
       <c r="AD447" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="448">
@@ -42964,7 +42964,7 @@
         <v>0.19</v>
       </c>
       <c r="AA448" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB448" t="n">
         <v>0.52</v>
@@ -42973,7 +42973,7 @@
         <v>3</v>
       </c>
       <c r="AD448" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="449">
@@ -43340,7 +43340,7 @@
         <v>0.38</v>
       </c>
       <c r="AA452" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB452" t="n">
         <v>0.67</v>
@@ -43349,7 +43349,7 @@
         <v>1</v>
       </c>
       <c r="AD452" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="453">
@@ -43434,7 +43434,7 @@
         <v>0.19</v>
       </c>
       <c r="AA453" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB453" t="n">
         <v>0.52</v>
@@ -43443,7 +43443,7 @@
         <v>2</v>
       </c>
       <c r="AD453" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="454">
@@ -43528,7 +43528,7 @@
         <v>0</v>
       </c>
       <c r="AA454" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="AB454" t="n">
         <v>0.4</v>
@@ -43537,7 +43537,7 @@
         <v>3</v>
       </c>
       <c r="AD454" t="n">
-        <v>0.102</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="455">
@@ -43725,7 +43725,7 @@
         <v>1</v>
       </c>
       <c r="AD456" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="457">
@@ -43819,7 +43819,7 @@
         <v>3</v>
       </c>
       <c r="AD457" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.6715</v>
       </c>
     </row>
     <row r="458">
@@ -44195,7 +44195,7 @@
         <v>3</v>
       </c>
       <c r="AD461" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="462">
@@ -44289,7 +44289,7 @@
         <v>1</v>
       </c>
       <c r="AD462" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="463">
@@ -44665,7 +44665,7 @@
         <v>3</v>
       </c>
       <c r="AD466" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="467">
@@ -44750,7 +44750,7 @@
         <v>0.64</v>
       </c>
       <c r="AA467" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AB467" t="n">
         <v>0.46</v>
@@ -44759,7 +44759,7 @@
         <v>1</v>
       </c>
       <c r="AD467" t="n">
-        <v>0.6240000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="468">
@@ -44844,7 +44844,7 @@
         <v>0.38</v>
       </c>
       <c r="AA468" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB468" t="n">
         <v>0.67</v>
@@ -44853,7 +44853,7 @@
         <v>2</v>
       </c>
       <c r="AD468" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="469">
@@ -44938,7 +44938,7 @@
         <v>0.19</v>
       </c>
       <c r="AA469" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB469" t="n">
         <v>0.52</v>
@@ -44947,7 +44947,7 @@
         <v>3</v>
       </c>
       <c r="AD469" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="470">
@@ -45135,7 +45135,7 @@
         <v>1</v>
       </c>
       <c r="AD471" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="472">
@@ -45229,7 +45229,7 @@
         <v>3</v>
       </c>
       <c r="AD472" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.6715</v>
       </c>
     </row>
     <row r="473">
@@ -45417,7 +45417,7 @@
         <v>2</v>
       </c>
       <c r="AD474" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="475">
@@ -45605,7 +45605,7 @@
         <v>1</v>
       </c>
       <c r="AD476" t="n">
-        <v>0.7615000000000001</v>
+        <v>0.7615</v>
       </c>
     </row>
     <row r="477">
@@ -45981,7 +45981,7 @@
         <v>2</v>
       </c>
       <c r="AD480" t="n">
-        <v>0.6729999999999999</v>
+        <v>0.673</v>
       </c>
     </row>
     <row r="481">
@@ -46066,7 +46066,7 @@
         <v>0.51</v>
       </c>
       <c r="AA481" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB481" t="n">
         <v>0.57</v>
@@ -46075,7 +46075,7 @@
         <v>3</v>
       </c>
       <c r="AD481" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="482">
@@ -46169,7 +46169,7 @@
         <v>1</v>
       </c>
       <c r="AD482" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="483">
@@ -46263,7 +46263,7 @@
         <v>2</v>
       </c>
       <c r="AD483" t="n">
-        <v>0.7370000000000001</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="484">
@@ -46348,7 +46348,7 @@
         <v>0.38</v>
       </c>
       <c r="AA484" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="AB484" t="n">
         <v>0.52</v>
@@ -46357,7 +46357,7 @@
         <v>3</v>
       </c>
       <c r="AD484" t="n">
-        <v>0.447</v>
+        <v>0.461</v>
       </c>
     </row>
     <row r="485">
@@ -46451,7 +46451,7 @@
         <v>1</v>
       </c>
       <c r="AD485" t="n">
-        <v>0.7555000000000001</v>
+        <v>0.7554999999999999</v>
       </c>
     </row>
     <row r="486">
@@ -46818,7 +46818,7 @@
         <v>0.54</v>
       </c>
       <c r="AA489" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AB489" t="n">
         <v>0.67</v>
@@ -46827,7 +46827,7 @@
         <v>2</v>
       </c>
       <c r="AD489" t="n">
-        <v>0.6035</v>
+        <v>0.6175</v>
       </c>
     </row>
     <row r="490">
@@ -46912,7 +46912,7 @@
         <v>0.13</v>
       </c>
       <c r="AA490" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AB490" t="n">
         <v>0.32</v>
@@ -46921,7 +46921,7 @@
         <v>3</v>
       </c>
       <c r="AD490" t="n">
-        <v>0.1235</v>
+        <v>0.1355</v>
       </c>
     </row>
     <row r="491">
@@ -47015,7 +47015,7 @@
         <v>1</v>
       </c>
       <c r="AD491" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="492">
@@ -47203,7 +47203,7 @@
         <v>3</v>
       </c>
       <c r="AD493" t="n">
-        <v>0.3995000000000001</v>
+        <v>0.3995</v>
       </c>
     </row>
     <row r="494">
@@ -47391,7 +47391,7 @@
         <v>2</v>
       </c>
       <c r="AD495" t="n">
-        <v>0.7174999999999999</v>
+        <v>0.7175</v>
       </c>
     </row>
     <row r="496">
@@ -47767,7 +47767,7 @@
         <v>3</v>
       </c>
       <c r="AD499" t="n">
-        <v>0.6365000000000001</v>
+        <v>0.6365</v>
       </c>
     </row>
     <row r="500">
@@ -48331,7 +48331,7 @@
         <v>3</v>
       </c>
       <c r="AD505" t="n">
-        <v>0.6465000000000001</v>
+        <v>0.6465</v>
       </c>
     </row>
     <row r="506">
@@ -48792,7 +48792,7 @@
         <v>0.64</v>
       </c>
       <c r="AA510" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AB510" t="n">
         <v>0.46</v>
@@ -48801,7 +48801,7 @@
         <v>2</v>
       </c>
       <c r="AD510" t="n">
-        <v>0.6519999999999999</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="511">
@@ -48886,7 +48886,7 @@
         <v>0.38</v>
       </c>
       <c r="AA511" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="AB511" t="n">
         <v>0.67</v>
@@ -48895,7 +48895,7 @@
         <v>3</v>
       </c>
       <c r="AD511" t="n">
-        <v>0.4965000000000001</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="512">
@@ -48980,7 +48980,7 @@
         <v>0.64</v>
       </c>
       <c r="AA512" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB512" t="n">
         <v>0.46</v>
@@ -48989,7 +48989,7 @@
         <v>1</v>
       </c>
       <c r="AD512" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="513">
@@ -49074,7 +49074,7 @@
         <v>0.51</v>
       </c>
       <c r="AA513" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB513" t="n">
         <v>0.57</v>
@@ -49083,7 +49083,7 @@
         <v>2</v>
       </c>
       <c r="AD513" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="514">
@@ -49168,7 +49168,7 @@
         <v>0.38</v>
       </c>
       <c r="AA514" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AB514" t="n">
         <v>0.67</v>
@@ -49177,7 +49177,7 @@
         <v>3</v>
       </c>
       <c r="AD514" t="n">
-        <v>0.5065000000000001</v>
+        <v>0.5185</v>
       </c>
     </row>
     <row r="515">
@@ -49356,7 +49356,7 @@
         <v>0.51</v>
       </c>
       <c r="AA516" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="AB516" t="n">
         <v>0.57</v>
@@ -49365,7 +49365,7 @@
         <v>2</v>
       </c>
       <c r="AD516" t="n">
-        <v>0.5950000000000001</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="517">
@@ -49450,7 +49450,7 @@
         <v>0.38</v>
       </c>
       <c r="AA517" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AB517" t="n">
         <v>0.67</v>
@@ -49459,7 +49459,7 @@
         <v>3</v>
       </c>
       <c r="AD517" t="n">
-        <v>0.4995000000000001</v>
+        <v>0.5135</v>
       </c>
     </row>
     <row r="518">
@@ -49544,7 +49544,7 @@
         <v>0.64</v>
       </c>
       <c r="AA518" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AB518" t="n">
         <v>0.46</v>
@@ -49553,7 +49553,7 @@
         <v>1</v>
       </c>
       <c r="AD518" t="n">
-        <v>0.6779999999999999</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="519">
@@ -49638,7 +49638,7 @@
         <v>0.51</v>
       </c>
       <c r="AA519" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AB519" t="n">
         <v>0.57</v>
@@ -49647,7 +49647,7 @@
         <v>2</v>
       </c>
       <c r="AD519" t="n">
-        <v>0.6090000000000001</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="520">
@@ -49732,7 +49732,7 @@
         <v>0.38</v>
       </c>
       <c r="AA520" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="AB520" t="n">
         <v>0.67</v>
@@ -49741,7 +49741,7 @@
         <v>3</v>
       </c>
       <c r="AD520" t="n">
-        <v>0.5185000000000001</v>
+        <v>0.5265</v>
       </c>
     </row>
     <row r="521">
@@ -49826,7 +49826,7 @@
         <v>0.74</v>
       </c>
       <c r="AA521" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB521" t="n">
         <v>0.46</v>
@@ -49835,7 +49835,7 @@
         <v>1</v>
       </c>
       <c r="AD521" t="n">
-        <v>0.73</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="522">
@@ -49920,7 +49920,7 @@
         <v>0.64</v>
       </c>
       <c r="AA522" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB522" t="n">
         <v>0.57</v>
@@ -49929,7 +49929,7 @@
         <v>2</v>
       </c>
       <c r="AD522" t="n">
-        <v>0.6835</v>
+        <v>0.6955</v>
       </c>
     </row>
     <row r="523">
@@ -50014,7 +50014,7 @@
         <v>0.54</v>
       </c>
       <c r="AA523" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AB523" t="n">
         <v>0.67</v>
@@ -50023,7 +50023,7 @@
         <v>3</v>
       </c>
       <c r="AD523" t="n">
-        <v>0.6075</v>
+        <v>0.6195000000000001</v>
       </c>
     </row>
     <row r="524">
@@ -50202,7 +50202,7 @@
         <v>0.51</v>
       </c>
       <c r="AA525" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AB525" t="n">
         <v>0.57</v>
@@ -50211,7 +50211,7 @@
         <v>2</v>
       </c>
       <c r="AD525" t="n">
-        <v>0.6080000000000001</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="526">
@@ -50296,7 +50296,7 @@
         <v>0.38</v>
       </c>
       <c r="AA526" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AB526" t="n">
         <v>0.67</v>
@@ -50305,7 +50305,7 @@
         <v>3</v>
       </c>
       <c r="AD526" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5255</v>
       </c>
     </row>
     <row r="527">
@@ -50493,7 +50493,7 @@
         <v>2</v>
       </c>
       <c r="AD528" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="529">
@@ -51057,7 +51057,7 @@
         <v>2</v>
       </c>
       <c r="AD534" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="535">
@@ -51339,7 +51339,7 @@
         <v>2</v>
       </c>
       <c r="AD537" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="538">
@@ -51527,7 +51527,7 @@
         <v>1</v>
       </c>
       <c r="AD539" t="n">
-        <v>0.7344999999999999</v>
+        <v>0.7345</v>
       </c>
     </row>
     <row r="540">
@@ -51988,7 +51988,7 @@
         <v>0.51</v>
       </c>
       <c r="AA544" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB544" t="n">
         <v>0.57</v>
@@ -51997,7 +51997,7 @@
         <v>3</v>
       </c>
       <c r="AD544" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="545">
@@ -52091,7 +52091,7 @@
         <v>2</v>
       </c>
       <c r="AD545" t="n">
-        <v>0.6764999999999999</v>
+        <v>0.6765</v>
       </c>
     </row>
     <row r="546">
@@ -52373,7 +52373,7 @@
         <v>1</v>
       </c>
       <c r="AD548" t="n">
-        <v>0.7699999999999999</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="549">
@@ -52467,7 +52467,7 @@
         <v>2</v>
       </c>
       <c r="AD549" t="n">
-        <v>0.5135000000000001</v>
+        <v>0.5135</v>
       </c>
     </row>
     <row r="550">
@@ -53125,7 +53125,7 @@
         <v>3</v>
       </c>
       <c r="AD556" t="n">
-        <v>0.5455000000000001</v>
+        <v>0.5455</v>
       </c>
     </row>
     <row r="557">
@@ -53219,7 +53219,7 @@
         <v>1</v>
       </c>
       <c r="AD557" t="n">
-        <v>0.6769999999999999</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="558">
@@ -53304,7 +53304,7 @@
         <v>0.64</v>
       </c>
       <c r="AA558" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB558" t="n">
         <v>0.46</v>
@@ -53313,7 +53313,7 @@
         <v>2</v>
       </c>
       <c r="AD558" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="559">
@@ -53398,7 +53398,7 @@
         <v>0.51</v>
       </c>
       <c r="AA559" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB559" t="n">
         <v>0.57</v>
@@ -53407,7 +53407,7 @@
         <v>3</v>
       </c>
       <c r="AD559" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="560">
@@ -53586,7 +53586,7 @@
         <v>0.51</v>
       </c>
       <c r="AA561" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AB561" t="n">
         <v>0.57</v>
@@ -53595,7 +53595,7 @@
         <v>2</v>
       </c>
       <c r="AD561" t="n">
-        <v>0.6080000000000001</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="562">
@@ -53680,7 +53680,7 @@
         <v>0.38</v>
       </c>
       <c r="AA562" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AB562" t="n">
         <v>0.67</v>
@@ -53689,7 +53689,7 @@
         <v>3</v>
       </c>
       <c r="AD562" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5255</v>
       </c>
     </row>
     <row r="563">
@@ -53971,7 +53971,7 @@
         <v>3</v>
       </c>
       <c r="AD565" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="566">
@@ -54065,7 +54065,7 @@
         <v>2</v>
       </c>
       <c r="AD566" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="567">
@@ -54159,7 +54159,7 @@
         <v>3</v>
       </c>
       <c r="AD567" t="n">
-        <v>0.7825000000000001</v>
+        <v>0.7825</v>
       </c>
     </row>
     <row r="568">
@@ -54535,7 +54535,7 @@
         <v>3</v>
       </c>
       <c r="AD571" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="572">
@@ -54629,7 +54629,7 @@
         <v>1</v>
       </c>
       <c r="AD572" t="n">
-        <v>0.7649999999999999</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="573">
@@ -54817,7 +54817,7 @@
         <v>3</v>
       </c>
       <c r="AD574" t="n">
-        <v>0.7069999999999999</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="575">
@@ -54911,7 +54911,7 @@
         <v>3</v>
       </c>
       <c r="AD575" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="576">
@@ -55005,7 +55005,7 @@
         <v>2</v>
       </c>
       <c r="AD576" t="n">
-        <v>0.8164999999999999</v>
+        <v>0.8165</v>
       </c>
     </row>
     <row r="577">
@@ -55381,7 +55381,7 @@
         <v>3</v>
       </c>
       <c r="AD580" t="n">
-        <v>0.7124999999999999</v>
+        <v>0.7125</v>
       </c>
     </row>
     <row r="581">
@@ -55475,7 +55475,7 @@
         <v>3</v>
       </c>
       <c r="AD581" t="n">
-        <v>0.8074999999999999</v>
+        <v>0.8075</v>
       </c>
     </row>
     <row r="582">
@@ -55569,7 +55569,7 @@
         <v>1</v>
       </c>
       <c r="AD582" t="n">
-        <v>0.8170000000000001</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="583">
@@ -55663,7 +55663,7 @@
         <v>2</v>
       </c>
       <c r="AD583" t="n">
-        <v>0.8139999999999998</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="584">
@@ -55757,7 +55757,7 @@
         <v>3</v>
       </c>
       <c r="AD584" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="585">
